--- a/backend/src/db/demo-docs/measurements-drifit-joggers.xlsx
+++ b/backend/src/db/demo-docs/measurements-drifit-joggers.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Poly Spandex Blend</t>
+          <t>88% Polyester 12% Spandex</t>
         </is>
       </c>
     </row>
@@ -653,19 +653,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D12" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>65.5</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="G12" s="5" t="n">
         <v>68.5</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="H12" s="5" t="n">
         <v>71.5</v>
       </c>
     </row>
@@ -714,19 +717,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>36.5</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <v>40</v>
       </c>
     </row>
@@ -743,19 +749,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E15" s="5" t="n">
         <v>26.5</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>27.5</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="G15" s="5" t="n">
         <v>28.5</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>29.5</v>
       </c>
     </row>
@@ -804,19 +813,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
+        <v>106</v>
+      </c>
+      <c r="E17" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>114</v>
       </c>
     </row>
@@ -961,19 +973,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="F22" s="5" t="n">
         <v>17.5</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="G22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="H22" s="5" t="n">
         <v>18.5</v>
       </c>
     </row>
@@ -990,19 +1005,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>33.5</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="F23" s="5" t="n">
         <v>34.5</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="G23" s="5" t="n">
         <v>35.5</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="H23" s="5" t="n">
         <v>36.5</v>
       </c>
     </row>
@@ -1019,7 +1037,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -1034,6 +1052,9 @@
       <c r="G24" s="5" t="n">
         <v>2.5</v>
       </c>
+      <c r="H24" s="5" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1112,19 +1133,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E27" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="F27" s="5" t="n">
         <v>14.5</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="G27" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="H27" s="5" t="n">
         <v>15.5</v>
       </c>
     </row>
@@ -1141,19 +1165,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>25.5</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="F28" s="5" t="n">
         <v>26.5</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="G28" s="5" t="n">
         <v>27.5</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="H28" s="5" t="n">
         <v>28.5</v>
       </c>
     </row>
